--- a/reports/ibis_files/arbel/arbel.xlsx
+++ b/reports/ibis_files/arbel/arbel.xlsx
@@ -119,7 +119,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12T22:46:14-05:00</t>
+          <t>2026-06-13T23:04:02-05:00</t>
         </is>
       </c>
     </row>
